--- a/docs/d/34/inyear.xlsx
+++ b/docs/d/34/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 88 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 87 clubs short</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1124,8 +1124,8 @@
       <c r="Y4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="9" t="n">
-        <v>0</v>
+      <c r="Z4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA4" s="10" t="n">
         <v>1</v>
@@ -2851,7 +2851,7 @@
         <v>1</v>
       </c>
       <c r="U21" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" s="9" t="n">
         <v>1</v>
@@ -6913,7 +6913,7 @@
         <v>1</v>
       </c>
       <c r="S61" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T61" s="10" t="n">
         <v>1</v>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>0</v>
@@ -7017,8 +7017,8 @@
       <c r="R62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S62" s="9" t="n">
-        <v>1</v>
+      <c r="S62" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T62" s="10" t="n">
         <v>1</v>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>0</v>
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7895,13 +7895,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7939,11 +7939,11 @@
       <c r="U71" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V71" s="9" t="n">
-        <v>3</v>
+      <c r="V71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>7</v>
@@ -9659,7 +9659,7 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="S120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T120" s="9" t="n">
         <v>0</v>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13440,8 +13440,8 @@
       <c r="T125" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U125" s="9" t="n">
-        <v>0</v>
+      <c r="U125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V125" s="9" t="n">
         <v>1</v>
@@ -13735,7 +13735,7 @@
         <v>2</v>
       </c>
       <c r="R128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S128" s="9" t="n">
         <v>0</v>
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15585,8 +15585,8 @@
       <c r="T146" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U146" s="9" t="n">
-        <v>0</v>
+      <c r="U146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V146" s="10" t="n">
         <v>4</v>
@@ -17420,7 +17420,7 @@
         <v>2</v>
       </c>
       <c r="Q164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R164" s="9" t="n">
         <v>0</v>
@@ -18159,7 +18159,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -18588,7 +18588,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -18654,7 +18654,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -19017,7 +19017,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -19182,7 +19182,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>

--- a/docs/d/34/inyear.xlsx
+++ b/docs/d/34/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,11 @@
       <c r="AB2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1234,7 +1238,11 @@
       <c r="AB5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1335,7 +1343,11 @@
       <c r="AB6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1642,7 +1654,11 @@
       <c r="AB9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1945,7 +1961,11 @@
       <c r="AB12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2874,7 +2894,11 @@
       <c r="AB21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3282,7 +3306,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3585,7 +3613,11 @@
       <c r="AB28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3686,7 +3718,11 @@
       <c r="AB29" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -4401,7 +4437,11 @@
       <c r="AB36" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC36" s="4" t="inlineStr"/>
+      <c r="AC36" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -4910,7 +4950,11 @@
       <c r="AB41" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC41" s="4" t="inlineStr"/>
+      <c r="AC41" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -5629,7 +5673,11 @@
       <c r="AB48" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC48" s="4" t="inlineStr"/>
+      <c r="AC48" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -6033,7 +6081,11 @@
       <c r="AB52" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC52" s="4" t="inlineStr"/>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6336,7 +6388,11 @@
       <c r="AB55" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC55" s="4" t="inlineStr"/>
+      <c r="AC55" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -6437,7 +6493,11 @@
       <c r="AB56" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC56" s="4" t="inlineStr"/>
+      <c r="AC56" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -7253,7 +7313,11 @@
       <c r="AB64" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC64" s="4" t="inlineStr"/>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7859,7 +7923,11 @@
       <c r="AB70" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC70" s="4" t="inlineStr"/>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -7960,7 +8028,11 @@
       <c r="AB71" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC71" s="4" t="inlineStr"/>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8166,7 +8238,11 @@
       <c r="AB73" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC73" s="4" t="inlineStr"/>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -8372,7 +8448,11 @@
       <c r="AB75" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8473,7 +8553,11 @@
       <c r="AB76" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC76" s="4" t="inlineStr"/>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -8574,7 +8658,11 @@
       <c r="AB77" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -9289,7 +9377,11 @@
       <c r="AB84" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC84" s="4" t="inlineStr"/>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -9697,7 +9789,11 @@
       <c r="AB88" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC88" s="4" t="inlineStr"/>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -10004,7 +10100,11 @@
       <c r="AB91" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC91" s="4" t="inlineStr"/>
+      <c r="AC91" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -10412,7 +10512,11 @@
       <c r="AB95" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC95" s="4" t="inlineStr"/>
+      <c r="AC95" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -10614,7 +10718,11 @@
       <c r="AB97" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC97" s="4" t="inlineStr"/>
+      <c r="AC97" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -11220,7 +11328,11 @@
       <c r="AB103" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC103" s="4" t="inlineStr"/>
+      <c r="AC103" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -11929,7 +12041,11 @@
       <c r="AB110" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC110" s="4" t="inlineStr"/>
+      <c r="AC110" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12135,7 +12251,11 @@
       <c r="AB112" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12236,7 +12356,11 @@
       <c r="AB113" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC113" s="4" t="inlineStr"/>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -13056,7 +13180,11 @@
       <c r="AB121" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC121" s="4" t="inlineStr"/>
+      <c r="AC121" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -13157,7 +13285,11 @@
       <c r="AB122" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC122" s="4" t="inlineStr"/>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13565,7 +13697,11 @@
       <c r="AB126" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC126" s="4" t="inlineStr"/>
+      <c r="AC126" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -13868,7 +14004,11 @@
       <c r="AB129" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC129" s="4" t="inlineStr"/>
+      <c r="AC129" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -13969,7 +14109,11 @@
       <c r="AB130" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC130" s="4" t="inlineStr"/>
+      <c r="AC130" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -14999,7 +15143,11 @@
       <c r="AB140" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC140" s="4" t="inlineStr"/>
+      <c r="AC140" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -15100,7 +15248,11 @@
       <c r="AB141" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC141" s="4" t="inlineStr"/>
+      <c r="AC141" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -15714,7 +15866,11 @@
       <c r="AB147" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC147" s="4" t="inlineStr"/>
+      <c r="AC147" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -16227,7 +16383,11 @@
       <c r="AB152" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC152" s="4" t="inlineStr"/>
+      <c r="AC152" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -16328,7 +16488,11 @@
       <c r="AB153" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC153" s="4" t="inlineStr"/>
+      <c r="AC153" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -16841,7 +17005,11 @@
       <c r="AB158" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC158" s="4" t="inlineStr"/>
+      <c r="AC158" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -17047,7 +17215,11 @@
       <c r="AB160" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC160" s="4" t="inlineStr"/>
+      <c r="AC160" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -17455,7 +17627,11 @@
       <c r="AB164" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC164" s="4" t="inlineStr"/>
+      <c r="AC164" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -17556,7 +17732,11 @@
       <c r="AB165" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC165" s="4" t="inlineStr"/>
+      <c r="AC165" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -17762,7 +17942,11 @@
       <c r="AB167" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC167" s="4" t="inlineStr"/>
+      <c r="AC167" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -17863,7 +18047,11 @@
       <c r="AB168" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC168" s="4" t="inlineStr"/>
+      <c r="AC168" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">

--- a/docs/d/34/inyear.xlsx
+++ b/docs/d/34/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 87 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 76 clubs short</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>1</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1851,8 +1851,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3091,8 +3091,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3590,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V28" s="9" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3915,8 +3915,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4121,8 +4121,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4428,8 +4428,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -5291,7 +5291,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5361,8 +5361,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5971,8 +5971,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -6533,13 +6533,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>4</v>
       </c>
       <c r="W68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X68" s="10" t="n">
         <v>7</v>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>1</v>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8106,8 +8106,8 @@
       <c r="S72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T72" s="9" t="n">
-        <v>0</v>
+      <c r="T72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U72" s="9" t="n">
         <v>0</v>
@@ -9092,7 +9092,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9147,8 +9147,8 @@
       <c r="T82" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U82" s="9" t="n">
-        <v>0</v>
+      <c r="U82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V82" s="9" t="n">
         <v>3</v>
@@ -9504,7 +9504,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9574,8 +9574,8 @@
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -11354,7 +11354,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11409,8 +11409,8 @@
       <c r="T104" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U104" s="9" t="n">
-        <v>0</v>
+      <c r="U104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V104" s="9" t="n">
         <v>0</v>
@@ -11655,7 +11655,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11725,8 +11725,8 @@
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -12423,7 +12423,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q114" s="10" t="n">
         <v>2</v>
@@ -13587,8 +13587,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="9" t="n">
         <v>0</v>
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13874,7 +13874,7 @@
         <v>1</v>
       </c>
       <c r="S128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128" s="9" t="n">
         <v>0</v>
@@ -13894,8 +13894,8 @@
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -14030,7 +14030,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14071,16 +14071,16 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S130" s="9" t="n">
-        <v>1</v>
+      <c r="S130" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T130" s="10" t="n">
         <v>1</v>
@@ -15219,7 +15219,7 @@
         <v>0</v>
       </c>
       <c r="S141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T141" s="9" t="n">
         <v>0</v>
@@ -15787,7 +15787,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15830,8 +15830,8 @@
       <c r="P147" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q147" s="9" t="n">
-        <v>0</v>
+      <c r="Q147" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>0</v>
@@ -18413,7 +18413,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -18479,7 +18479,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -18545,7 +18545,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -18578,7 +18578,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -18644,7 +18644,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -18710,7 +18710,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -18875,7 +18875,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -18941,7 +18941,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -18974,7 +18974,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19073,7 +19073,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19106,7 +19106,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -19238,13 +19238,13 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -19370,7 +19370,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>

--- a/docs/d/34/inyear.xlsx
+++ b/docs/d/34/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 76 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -1023,8 +1023,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="9" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="P5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="9" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1412,8 +1412,8 @@
       <c r="P7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" s="9" t="n">
-        <v>1</v>
+      <c r="Q7" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R7" s="9" t="n">
         <v>0</v>
@@ -1421,8 +1421,8 @@
       <c r="S7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="T7" s="9" t="n">
-        <v>0</v>
+      <c r="T7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U7" s="9" t="n">
         <v>0</v>
@@ -1439,8 +1439,8 @@
       <c r="Y7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="9" t="n">
-        <v>0</v>
+      <c r="Z7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA7" s="10" t="n">
         <v>1</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1544,8 +1544,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1615,8 +1615,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P9" s="9" t="n">
-        <v>3</v>
+      <c r="P9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q9" s="10" t="n">
         <v>2</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1750,8 +1750,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="10" t="n">
         <v>2</v>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="9" t="n">
         <v>0</v>
@@ -2162,8 +2162,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2267,8 +2267,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="9" t="n">
         <v>0</v>
@@ -2368,8 +2368,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="9" t="n">
         <v>0</v>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2455,11 +2455,11 @@
       <c r="S17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="9" t="n">
-        <v>0</v>
+      <c r="T17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>3</v>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3270,8 +3270,8 @@
       <c r="P25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q25" s="9" t="n">
-        <v>1</v>
+      <c r="Q25" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R25" s="9" t="n">
         <v>0</v>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3503,8 +3503,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3604,8 +3604,8 @@
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3814,8 +3814,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -4327,8 +4327,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="9" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>6</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>0</v>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4634,8 +4634,8 @@
       <c r="Y38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" s="9" t="n">
-        <v>0</v>
+      <c r="Z38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA38" s="10" t="n">
         <v>1</v>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4840,8 +4840,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -5046,8 +5046,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="9" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5238,11 +5238,11 @@
       <c r="S44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="9" t="n">
-        <v>0</v>
+      <c r="T44" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V44" s="9" t="n">
         <v>2</v>
@@ -5256,8 +5256,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5608,13 +5608,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5664,8 +5664,8 @@
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" s="9" t="n">
-        <v>0</v>
+      <c r="Z48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA48" s="10" t="n">
         <v>1</v>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="P55" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q55" s="10" t="n">
         <v>2</v>
@@ -6519,7 +6519,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6589,8 +6589,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q61" s="10" t="n">
         <v>2</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7199,8 +7199,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -7339,7 +7339,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7409,8 +7409,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7510,8 +7510,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="9" t="n">
         <v>0</v>
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7591,13 +7591,13 @@
         <v>0</v>
       </c>
       <c r="S67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T67" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V67" s="9" t="n">
         <v>2</v>
@@ -7611,8 +7611,8 @@
       <c r="Y67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" s="9" t="n">
-        <v>0</v>
+      <c r="Z67" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA67" s="10" t="n">
         <v>1</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7656,13 +7656,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7691,8 +7691,8 @@
       <c r="R68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S68" s="9" t="n">
-        <v>1</v>
+      <c r="S68" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T68" s="9" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
         <v>4</v>
       </c>
       <c r="W68" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X68" s="10" t="n">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7813,8 +7813,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8095,10 +8095,10 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q72" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
@@ -8109,8 +8109,8 @@
       <c r="T72" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U72" s="9" t="n">
-        <v>0</v>
+      <c r="U72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V72" s="9" t="n">
         <v>2</v>
@@ -8264,7 +8264,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8334,8 +8334,8 @@
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8383,13 +8383,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8427,11 +8427,11 @@
       <c r="U75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V75" s="9" t="n">
-        <v>3</v>
+      <c r="V75" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X75" s="10" t="n">
         <v>7</v>
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8859,8 +8859,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -9348,7 +9348,7 @@
         <v>0</v>
       </c>
       <c r="S84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84" s="10" t="n">
         <v>1</v>
@@ -9504,7 +9504,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9545,7 +9545,7 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" s="9" t="n">
         <v>0</v>
@@ -9559,8 +9559,8 @@
       <c r="T86" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U86" s="9" t="n">
-        <v>0</v>
+      <c r="U86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V86" s="9" t="n">
         <v>2</v>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9750,8 +9750,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P88" s="9" t="n">
-        <v>3</v>
+      <c r="P88" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>0</v>
@@ -9990,8 +9990,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="9" t="n">
         <v>0</v>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10062,13 +10062,13 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R91" s="9" t="n">
-        <v>1</v>
+      <c r="R91" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S91" s="9" t="n">
         <v>1</v>
@@ -10332,7 +10332,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10402,8 +10402,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10683,7 +10683,7 @@
         <v>0</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
@@ -11047,7 +11047,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11117,8 +11117,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11148,7 +11148,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11218,8 +11218,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11249,7 +11249,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11304,8 +11304,8 @@
       <c r="T103" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U103" s="9" t="n">
-        <v>0</v>
+      <c r="U103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V103" s="9" t="n">
         <v>2</v>
@@ -11354,7 +11354,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11424,8 +11424,8 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -11523,8 +11523,8 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="9" t="n">
         <v>0</v>
@@ -11756,7 +11756,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11826,8 +11826,8 @@
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
@@ -12172,7 +12172,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12224,8 +12224,8 @@
       <c r="S112" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T112" s="9" t="n">
-        <v>0</v>
+      <c r="T112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
@@ -12382,7 +12382,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12429,7 +12429,7 @@
         <v>2</v>
       </c>
       <c r="R114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S114" s="9" t="n">
         <v>0</v>
@@ -12452,8 +12452,8 @@
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
@@ -12487,7 +12487,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12557,8 +12557,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12588,7 +12588,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12658,8 +12658,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -12689,7 +12689,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12759,8 +12759,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -13101,7 +13101,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13153,8 +13153,8 @@
       <c r="S121" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="T121" s="9" t="n">
-        <v>0</v>
+      <c r="T121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U121" s="9" t="n">
         <v>0</v>
@@ -13416,7 +13416,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13486,8 +13486,8 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13659,7 +13659,7 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q126" s="9" t="n">
         <v>1</v>
@@ -13670,8 +13670,8 @@
       <c r="S126" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T126" s="9" t="n">
-        <v>0</v>
+      <c r="T126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U126" s="9" t="n">
         <v>0</v>
@@ -14080,7 +14080,7 @@
         <v>0</v>
       </c>
       <c r="S130" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T130" s="10" t="n">
         <v>1</v>
@@ -14135,7 +14135,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14205,8 +14205,8 @@
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -14236,7 +14236,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14306,8 +14306,8 @@
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -14341,7 +14341,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14411,8 +14411,8 @@
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -14442,7 +14442,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14494,8 +14494,8 @@
       <c r="S134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T134" s="9" t="n">
-        <v>0</v>
+      <c r="T134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U134" s="9" t="n">
         <v>0</v>
@@ -14512,8 +14512,8 @@
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -14854,7 +14854,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14924,8 +14924,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -15105,7 +15105,7 @@
         </is>
       </c>
       <c r="P140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q140" s="9" t="n">
         <v>0</v>
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15344,8 +15344,8 @@
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15445,8 +15445,8 @@
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="9" t="n">
-        <v>0</v>
+      <c r="Z143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15651,8 +15651,8 @@
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
@@ -15936,7 +15936,7 @@
         <v>2</v>
       </c>
       <c r="Q148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -16269,8 +16269,8 @@
       <c r="Y151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z151" s="9" t="n">
-        <v>0</v>
+      <c r="Z151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA151" s="10" t="n">
         <v>1</v>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -16374,8 +16374,8 @@
       <c r="Y152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z152" s="9" t="n">
-        <v>0</v>
+      <c r="Z152" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA152" s="10" t="n">
         <v>1</v>
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16770,13 +16770,13 @@
         <v>0</v>
       </c>
       <c r="S156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T156" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U156" s="9" t="n">
-        <v>0</v>
+      <c r="U156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V156" s="9" t="n">
         <v>2</v>
@@ -16926,7 +16926,7 @@
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -16996,8 +16996,8 @@
       <c r="Y158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z158" s="9" t="n">
-        <v>0</v>
+      <c r="Z158" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA158" s="10" t="n">
         <v>1</v>
@@ -17031,7 +17031,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -17101,8 +17101,8 @@
       <c r="Y159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z159" s="9" t="n">
-        <v>0</v>
+      <c r="Z159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA159" s="10" t="n">
         <v>1</v>
@@ -17136,7 +17136,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -17206,8 +17206,8 @@
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="9" t="n">
-        <v>0</v>
+      <c r="Z160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA160" s="10" t="n">
         <v>1</v>
@@ -17241,7 +17241,7 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -17290,8 +17290,8 @@
       <c r="R161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S161" s="9" t="n">
-        <v>1</v>
+      <c r="S161" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T161" s="9" t="n">
         <v>0</v>
@@ -17447,7 +17447,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -17517,8 +17517,8 @@
       <c r="Y163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="9" t="n">
-        <v>0</v>
+      <c r="Z163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA163" s="10" t="n">
         <v>1</v>
@@ -17548,7 +17548,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -17591,8 +17591,8 @@
       <c r="P164" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q164" s="9" t="n">
-        <v>1</v>
+      <c r="Q164" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R164" s="9" t="n">
         <v>0</v>
@@ -17863,7 +17863,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17912,8 +17912,8 @@
       <c r="R167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S167" s="9" t="n">
-        <v>1</v>
+      <c r="S167" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T167" s="9" t="n">
         <v>0</v>
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>10</v>
@@ -18143,8 +18143,8 @@
       <c r="Y169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z169" s="9" t="n">
-        <v>0</v>
+      <c r="Z169" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA169" s="10" t="n">
         <v>1</v>
@@ -18219,7 +18219,7 @@
         </is>
       </c>
       <c r="P170" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q170" s="9" t="n">
         <v>0</v>
@@ -18380,13 +18380,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -18413,7 +18413,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -18446,7 +18446,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -18512,7 +18512,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -18545,7 +18545,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -18611,7 +18611,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -18644,7 +18644,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -18677,7 +18677,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -18743,7 +18743,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -18776,7 +18776,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -18809,7 +18809,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -18875,7 +18875,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -18908,7 +18908,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -18974,7 +18974,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19007,7 +19007,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -19073,7 +19073,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19106,7 +19106,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -19139,7 +19139,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -19172,7 +19172,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -19205,13 +19205,13 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -19238,7 +19238,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -19271,7 +19271,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -19304,7 +19304,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -19337,7 +19337,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -19403,7 +19403,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -19436,7 +19436,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -19469,7 +19469,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -19502,7 +19502,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>

--- a/docs/d/34/inyear.xlsx
+++ b/docs/d/34/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/34/inyear.xlsx
+++ b/docs/d/34/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/34/inyear.xlsx
+++ b/docs/d/34/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/34/inyear.xlsx
+++ b/docs/d/34/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/34/inyear.xlsx
+++ b/docs/d/34/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
@@ -1116,8 +1116,8 @@
       <c r="U4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="9" t="n">
-        <v>1</v>
+      <c r="V4" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         <v>2</v>
       </c>
       <c r="R13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T13" s="10" t="n">
         <v>1</v>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2100,17 +2100,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M14" s="7" t="n">
@@ -2144,11 +2144,11 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>3</v>
+      <c r="V14" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>7</v>
@@ -2621,13 +2621,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -2766,8 +2766,8 @@
       <c r="U20" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V20" s="9" t="n">
-        <v>3</v>
+      <c r="V20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -3062,8 +3062,8 @@
       <c r="P23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" s="9" t="n">
-        <v>1</v>
+      <c r="Q23" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R23" s="9" t="n">
         <v>0</v>
@@ -3077,8 +3077,8 @@
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>3</v>
+      <c r="V23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3546,13 +3546,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3593,8 +3593,8 @@
       <c r="V28" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W28" s="9" t="n">
-        <v>1</v>
+      <c r="W28" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X28" s="10" t="n">
         <v>6</v>
@@ -3647,13 +3647,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>2</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -4576,13 +4576,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5022,8 +5022,8 @@
       <c r="S42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="9" t="n">
-        <v>0</v>
+      <c r="T42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U42" s="9" t="n">
         <v>0</v>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5299,13 +5299,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5343,8 +5343,8 @@
       <c r="U45" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>3</v>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5404,13 +5404,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5636,13 +5636,13 @@
         <v>0</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S48" s="9" t="n">
-        <v>1</v>
+      <c r="S48" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T48" s="10" t="n">
         <v>1</v>
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q49" s="10" t="n">
         <v>2</v>
@@ -6422,13 +6422,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6464,13 +6464,13 @@
         <v>1</v>
       </c>
       <c r="U56" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V56" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W56" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>6</v>
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -7347,13 +7347,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -8167,13 +8167,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8313,8 +8313,8 @@
       <c r="T74" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U74" s="9" t="n">
-        <v>0</v>
+      <c r="U74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V74" s="9" t="n">
         <v>1</v>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>2</v>
       </c>
       <c r="R76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76" s="9" t="n">
         <v>1</v>
@@ -8587,13 +8587,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>7</v>
@@ -8692,13 +8692,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>4</v>
       </c>
       <c r="W78" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X78" s="10" t="n">
         <v>7</v>
@@ -9205,13 +9205,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>4</v>
       </c>
       <c r="W83" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X83" s="10" t="n">
         <v>7</v>
@@ -9516,13 +9516,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X86" s="9" t="n">
         <v>0</v>
@@ -9809,7 +9809,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9823,13 +9823,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L89" s="8" t="inlineStr">
         <is>
@@ -9864,8 +9864,8 @@
       <c r="T89" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U89" s="9" t="n">
-        <v>0</v>
+      <c r="U89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V89" s="9" t="n">
         <v>2</v>
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11494,7 +11494,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -11502,14 +11502,14 @@
       <c r="R105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S105" s="9" t="n">
-        <v>0</v>
+      <c r="S105" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T105" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U105" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V105" s="9" t="n">
         <v>0</v>
@@ -11667,13 +11667,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -12075,13 +12075,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q111" s="10" t="n">
         <v>2</v>
@@ -12123,7 +12123,7 @@
         <v>4</v>
       </c>
       <c r="W111" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X111" s="10" t="n">
         <v>7</v>
@@ -12207,7 +12207,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -12390,13 +12390,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T118" s="10" t="n">
         <v>1</v>
@@ -13729,13 +13729,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L127" s="8" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>1</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13830,13 +13830,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>4</v>
       </c>
       <c r="W128" s="10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>4</v>
@@ -13935,13 +13935,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L129" s="8" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>4</v>
       </c>
       <c r="W129" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X129" s="10" t="n">
         <v>5</v>
@@ -14448,13 +14448,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -14856,13 +14856,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L138" s="8" t="inlineStr">
         <is>
@@ -15587,13 +15587,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L145" s="8" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         </is>
       </c>
       <c r="P145" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q145" s="9" t="n">
         <v>0</v>
@@ -15632,7 +15632,7 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -16090,7 +16090,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -16104,13 +16104,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L150" s="8" t="inlineStr">
         <is>
@@ -16139,8 +16139,8 @@
       <c r="R150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S150" s="9" t="n">
-        <v>1</v>
+      <c r="S150" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T150" s="9" t="n">
         <v>0</v>
@@ -16149,7 +16149,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -16239,7 +16239,7 @@
         <v>0</v>
       </c>
       <c r="Q151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>0</v>
@@ -16251,7 +16251,7 @@
         <v>1</v>
       </c>
       <c r="U151" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V151" s="9" t="n">
         <v>2</v>
@@ -16857,7 +16857,7 @@
         <v>2</v>
       </c>
       <c r="Q157" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R157" s="9" t="n">
         <v>0</v>
@@ -17033,13 +17033,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L159" s="8" t="inlineStr">
         <is>
@@ -17138,13 +17138,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L160" s="8" t="inlineStr">
         <is>
@@ -17760,13 +17760,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="L166" s="8" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>4</v>
       </c>
       <c r="W166" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X166" s="10" t="n">
         <v>7</v>
@@ -17865,13 +17865,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         </is>
       </c>
       <c r="P168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q168" s="9" t="n">
         <v>1</v>
@@ -18180,13 +18180,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         </is>
       </c>
       <c r="P170" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q170" s="9" t="n">
         <v>1</v>
@@ -18228,7 +18228,7 @@
         <v>4</v>
       </c>
       <c r="W170" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X170" s="10" t="n">
         <v>5</v>
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -18285,13 +18285,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L171" s="8" t="inlineStr">
         <is>
@@ -18311,11 +18311,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P171" s="9" t="n">
-        <v>3</v>
+      <c r="P171" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q171" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R171" s="9" t="n">
         <v>0</v>
@@ -18545,7 +18545,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -18611,7 +18611,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -18626,7 +18626,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -18644,7 +18644,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -18677,7 +18677,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -18710,7 +18710,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -18809,7 +18809,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -18875,7 +18875,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -19073,7 +19073,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -19172,13 +19172,13 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19568,7 +19568,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -19700,7 +19700,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>

--- a/docs/d/34/inyear.xlsx
+++ b/docs/d/34/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>0</v>
@@ -2100,13 +2100,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>7</v>
@@ -2516,17 +2516,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M18" s="7" t="n">
@@ -2752,7 +2752,7 @@
         <v>3</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="9" t="n">
         <v>0</v>
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -3134,13 +3134,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>1</v>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3787,14 +3787,14 @@
       <c r="R30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="9" t="n">
-        <v>1</v>
+      <c r="S30" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U30" s="9" t="n">
-        <v>0</v>
+      <c r="U30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V30" s="9" t="n">
         <v>3</v>
@@ -4576,13 +4576,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
@@ -4677,13 +4677,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4924,8 +4924,8 @@
       <c r="T41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U41" s="9" t="n">
-        <v>0</v>
+      <c r="U41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V41" s="9" t="n">
         <v>1</v>
@@ -4984,13 +4984,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>5</v>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5633,16 +5633,16 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q48" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S48" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T48" s="10" t="n">
         <v>1</v>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
@@ -5733,8 +5733,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P49" s="9" t="n">
-        <v>3</v>
+      <c r="P49" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q49" s="10" t="n">
         <v>2</v>
@@ -6408,7 +6408,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6422,13 +6422,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6469,8 +6469,8 @@
       <c r="V56" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W56" s="9" t="n">
-        <v>3</v>
+      <c r="W56" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>6</v>
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7062,8 +7062,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P62" s="9" t="n">
-        <v>3</v>
+      <c r="P62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q62" s="10" t="n">
         <v>2</v>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7347,17 +7347,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L65" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M65" s="7" t="n">
@@ -7385,8 +7385,8 @@
       <c r="S65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T65" s="9" t="n">
-        <v>0</v>
+      <c r="T65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U65" s="9" t="n">
         <v>0</v>
@@ -7755,13 +7755,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
@@ -8167,13 +8167,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X73" s="10" t="n">
         <v>7</v>
@@ -8272,13 +8272,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>1</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8692,13 +8692,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
@@ -9411,13 +9411,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X85" s="10" t="n">
         <v>7</v>
@@ -9516,13 +9516,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X86" s="9" t="n">
         <v>0</v>
@@ -9964,7 +9964,7 @@
         <v>0</v>
       </c>
       <c r="S90" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T90" s="10" t="n">
         <v>1</v>
@@ -10239,13 +10239,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L93" s="8" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="8" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>1</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -11667,13 +11667,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
@@ -12075,13 +12075,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12495,13 +12495,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L115" s="8" t="inlineStr">
         <is>
@@ -12600,13 +12600,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>1</v>
       </c>
       <c r="U123" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V123" s="10" t="n">
         <v>4</v>
@@ -13655,7 +13655,7 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q126" s="9" t="n">
         <v>1</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="S126" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T126" s="9" t="n">
         <v>0</v>
@@ -13715,7 +13715,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13756,10 +13756,10 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q127" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q127" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13830,13 +13830,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>4</v>
       </c>
       <c r="W128" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>4</v>
@@ -13971,7 +13971,7 @@
         <v>0</v>
       </c>
       <c r="S129" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T129" s="9" t="n">
         <v>0</v>
@@ -14063,7 +14063,7 @@
         </is>
       </c>
       <c r="P130" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q130" s="10" t="n">
         <v>2</v>
@@ -14123,7 +14123,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14164,10 +14164,10 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q131" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q131" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>0</v>
@@ -14553,13 +14553,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L135" s="8" t="inlineStr">
         <is>
@@ -14654,13 +14654,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="8" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>1</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -15573,7 +15573,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15587,13 +15587,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L145" s="8" t="inlineStr">
         <is>
@@ -15625,8 +15625,8 @@
       <c r="S145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T145" s="9" t="n">
-        <v>0</v>
+      <c r="T145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U145" s="9" t="n">
         <v>0</v>
@@ -16032,7 +16032,7 @@
         <v>2</v>
       </c>
       <c r="R149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S149" s="10" t="n">
         <v>2</v>
@@ -17019,7 +17019,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -17033,13 +17033,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L159" s="8" t="inlineStr">
         <is>
@@ -17077,8 +17077,8 @@
       <c r="U159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V159" s="9" t="n">
-        <v>3</v>
+      <c r="V159" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W159" s="9" t="n">
         <v>0</v>
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L172" s="8" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -18743,13 +18743,13 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -18809,7 +18809,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -18875,13 +18875,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -18941,7 +18941,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -18974,7 +18974,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -19007,7 +19007,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -19022,7 +19022,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -19403,7 +19403,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -19436,13 +19436,13 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -19535,7 +19535,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -19634,7 +19634,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
